--- a/output/2026-09-14_20_Croazia_Virovitico-podravska_Cleaning.xlsx
+++ b/output/2026-09-14_20_Croazia_Virovitico-podravska_Cleaning.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sede a Bjelovar, fuori dalla contea. Il sito aziendale si dichiara unico rappresentante specializzato per la contea di Bjelovar-Bilogora e area limitrofa (Virovitica, Slatina, Đurđevac); nessun punto vendita fisico confermato in Virovitičko-podravska.</t>
+          <t>Sede a Bjelovar, fuori dalla contea. Il sito aziendale si dichiara unico rappresentante specializzato per la contea di Bjelovar-Bilogora e area limitrofa (Virovitica, Slatina, Đurđevac); nessun punto vendita fisico confermato in Virovitičko-podravska. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sede a Zagabria, fuori dalla contea. Distributore nazionale leader di settore con vendita/spedizione su tutta la Croazia; nessuna filiale fisica confermata in Virovitičko-podravska.</t>
+          <t>Sede a Zagabria, fuori dalla contea. Distributore nazionale leader di settore con vendita/spedizione su tutta la Croazia; nessuna filiale fisica confermata in Virovitičko-podravska. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-14_20_Croazia_Virovitico-podravska_Cleaning.xlsx
+++ b/output/2026-09-14_20_Croazia_Virovitico-podravska_Cleaning.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
